--- a/results/Int All Data 0.2/Rando_1_permute.xlsx
+++ b/results/Int All Data 0.2/Rando_1_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8833212353303539</v>
+        <v>0.9115768079321047</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8858057073800434</v>
+        <v>0.9099975280837156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9025248859191016</v>
+        <v>0.9096816721140377</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8783330652154295</v>
+        <v>0.9103027901264601</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8823332535519083</v>
+        <v>0.9130925242188941</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8450979545873665</v>
+        <v>0.9130925242188941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8550570306399909</v>
+        <v>0.9143347602437388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8535095325724016</v>
+        <v>0.9037651601056254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8550570306399909</v>
+        <v>0.9050073961304701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8541094627309574</v>
+        <v>0.905291470319348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8326755943389192</v>
+        <v>0.9059231822587037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8447820986176887</v>
+        <v>0.9049862082766036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8485194006191562</v>
+        <v>0.9043544963372478</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8485194006191562</v>
+        <v>0.9043544963372478</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8382550625237872</v>
+        <v>0.9074283046185598</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8382550625237872</v>
+        <v>0.9077441605882376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8410447966162213</v>
+        <v>0.9001530233890365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8472559767404448</v>
+        <v>0.9001530233890365</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8429611202881548</v>
+        <v>0.9026586832925925</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8152948839180265</v>
+        <v>0.9067754048253376</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8127998179414038</v>
+        <v>0.9067754048253376</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8127998179414038</v>
+        <v>0.9043121206295146</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.811557581916559</v>
+        <v>0.9070806668680821</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.811557581916559</v>
+        <v>0.9064489549287265</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8218431078657946</v>
+        <v>0.9086599467164712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8196533039319163</v>
+        <v>0.90010005375437</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8196533039319163</v>
+        <v>0.8985631496137141</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.819032185919494</v>
+        <v>0.8957840094482133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8212008019995056</v>
+        <v>0.893299537398524</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8230853438906394</v>
+        <v>0.8917308514770681</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8249486979279064</v>
+        <v>0.8800885181450426</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8252751478245175</v>
+        <v>0.8928267343631676</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8252751478245175</v>
+        <v>0.8862996982692662</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8246540298120951</v>
+        <v>0.8791091684552093</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8234011998603171</v>
+        <v>0.8791091684552093</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8150108097291486</v>
+        <v>0.8791091684552093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8146737659056043</v>
+        <v>0.8835311520306988</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8143473160089931</v>
+        <v>0.8533910375378144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.81524191428336</v>
+        <v>0.8484009055845689</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.817421124290305</v>
+        <v>0.8456217654190683</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8366545948215316</v>
+        <v>0.8668013795647074</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8419182070367217</v>
+        <v>0.8723278781149089</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8596147734272923</v>
+        <v>0.8814771073086325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8710789718397727</v>
+        <v>0.8802348712837877</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8773113398178629</v>
+        <v>0.8774239493374871</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8505926713567682</v>
+        <v>0.8774239493374871</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8527824752906463</v>
+        <v>0.8644844485076295</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8527824752906463</v>
+        <v>0.8622734567198849</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8527824752906463</v>
+        <v>0.8622734567198849</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8445258825329687</v>
+        <v>0.864463260653763</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8642321560995515</v>
+        <v>0.8613682645185845</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8716008208331535</v>
+        <v>0.8613682645185845</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8716008208331535</v>
+        <v>0.8667695977839074</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8854984834989779</v>
+        <v>0.858347425871939</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8719908342913645</v>
+        <v>0.8599267057203281</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8757811059274982</v>
+        <v>0.8487889572044589</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8440895696903827</v>
+        <v>0.8280907781827884</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8487956274547502</v>
+        <v>0.8290171582379553</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8262639143382915</v>
+        <v>0.7899887390480376</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8247164162707024</v>
+        <v>0.7440624963215532</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8250322722403801</v>
+        <v>0.7388200719602296</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8000200107508739</v>
+        <v>0.7413575136445856</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8050929322812648</v>
+        <v>0.7438419856942751</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7961343937723404</v>
+        <v>0.7416521817603967</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7964502497420183</v>
+        <v>0.7725915491852486</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7895226062629727</v>
+        <v>0.7725915491852486</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7897854925979839</v>
+        <v>0.7732232611246042</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7904172045373397</v>
+        <v>0.6922150331746859</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7701706406971589</v>
+        <v>0.6957000427680754</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7807845783813265</v>
+        <v>0.6938684705116083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7943114536044855</v>
+        <v>0.6957424184758085</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8160419519506559</v>
+        <v>0.6156825431702522</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.814399108540667</v>
+        <v>0.6156825431702522</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8169577380788895</v>
+        <v>0.6286220440001098</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8097883961186991</v>
+        <v>0.6372455005238109</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8097883961186991</v>
+        <v>0.6372349065968775</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7816348391096393</v>
+        <v>0.6517835072176033</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7841828747209285</v>
+        <v>0.6463503921714804</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7873414344177068</v>
+        <v>0.6435394702251798</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7825930009456061</v>
+        <v>0.6433401474517682</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7376461079089549</v>
+        <v>0.6348438180512668</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7326136002479764</v>
+        <v>0.636107241929978</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7312654249537986</v>
+        <v>0.6460345362018025</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7346955030742006</v>
+        <v>0.6500771002460145</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7346955030742006</v>
+        <v>0.672562513978098</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7407285482788792</v>
+        <v>0.6845014772642557</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7385175564911344</v>
+        <v>0.6848173332339336</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7241345350246995</v>
+        <v>0.690557672161122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7231869671156661</v>
+        <v>0.7109082134323146</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7069935612466305</v>
+        <v>0.7209818608428842</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7060459933375971</v>
+        <v>0.5865716090605541</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7089840424070971</v>
+        <v>0.5728116674448626</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6909484703546611</v>
+        <v>0.5526219969159902</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6830202893319156</v>
+        <v>0.5701596544025613</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6954022357109506</v>
+        <v>0.5701596544025613</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6925595319838501</v>
+        <v>0.5780011221715196</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.692875387953528</v>
+        <v>0.5780011221715196</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6919278200444945</v>
+        <v>0.5573009813115282</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6839486312254035</v>
+        <v>0.5547741335541055</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6980263906490938</v>
+        <v>0.5673891463256731</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6986369147345829</v>
+        <v>0.5486900805530814</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7166195171523524</v>
+        <v>0.5187155452144878</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7172512290917081</v>
+        <v>0.5319179323793568</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6874210850535386</v>
+        <v>0.5363293220279131</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6874210850535386</v>
+        <v>0.5264742234063007</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6874210850535386</v>
+        <v>0.5252107995275893</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7063406614534082</v>
+        <v>0.5095027524591643</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6965173446125958</v>
+        <v>0.5100603069099869</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6965173446125958</v>
+        <v>0.5105138839297976</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6965173446125958</v>
+        <v>0.5105138839297976</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6828613804279162</v>
+        <v>0.5021956894488411</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6806609825671046</v>
+        <v>0.5028168074612634</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6888732377787281</v>
+        <v>0.5135559104303096</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6981178123148515</v>
+        <v>0.5091021450740202</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7054884388867745</v>
+        <v>0.5094180010436981</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7017723247391736</v>
+        <v>0.5131341151912988</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6973927168714172</v>
+        <v>0.5115972110506429</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6958346248768946</v>
+        <v>0.5052694977301531</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6974033107983505</v>
+        <v>0.5093438435551649</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6983614726343172</v>
+        <v>0.5375609641258244</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7137999631174397</v>
+        <v>0.5396342348634364</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.692315086929056</v>
+        <v>0.5404162236181792</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6578954183227852</v>
+        <v>0.5516194975339692</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6662116509654207</v>
+        <v>0.5474815881473576</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6595786756021863</v>
+        <v>0.5595245288645272</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6621902747750752</v>
+        <v>0.5585769609554938</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6621902747750752</v>
+        <v>0.5585769609554938</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6688762197729761</v>
+        <v>0.5401023294868224</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6732876094215323</v>
+        <v>0.5394302036780545</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6675386384057317</v>
+        <v>0.5401294028556518</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6778665400627004</v>
+        <v>0.5401082150017853</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6772348281233447</v>
+        <v>0.5400870271479187</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6772560159772113</v>
+        <v>0.5835499856785802</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6885440413084677</v>
+        <v>0.5844975535876138</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6480595457167184</v>
+        <v>0.5774765266044894</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6496388255651075</v>
+        <v>0.5864178009361892</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6426688063783288</v>
+        <v>0.5808913023859877</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.6129889391555463</v>
+        <v>0.5802595904466321</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5967743454326442</v>
+        <v>0.6255031134374154</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5967743454326442</v>
+        <v>0.6184291168196246</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6170315031997583</v>
+        <v>0.6186457037702608</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.6458803357097734</v>
+        <v>0.6229087784417511</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.6776268034198765</v>
+        <v>0.6174207319226408</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.6855655783695553</v>
+        <v>0.5949333563522363</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.6858814343392332</v>
+        <v>0.5722831482011904</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.6470503760844062</v>
+        <v>0.5499856785802568</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5492652915487929</v>
+        <v>0.5306933528994009</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5334022592530104</v>
+        <v>0.5109957114214303</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5305654410408729</v>
+        <v>0.5529052863695397</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5116776464218031</v>
+        <v>0.5693172410275325</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5116776464218031</v>
+        <v>0.5341917029933729</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5074145717503129</v>
+        <v>0.5341917029933729</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5041434025339104</v>
+        <v>0.498523128111966</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5052796992894222</v>
+        <v>0.4943765866367421</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4992168341422647</v>
+        <v>0.4941242942286641</v>
       </c>
     </row>
   </sheetData>
